--- a/SINGLE HADITH CONTENT/missing_input/[V1] BULUGH AL MARAM-(TAWHEED)-BANGLA_missing.xlsx
+++ b/SINGLE HADITH CONTENT/missing_input/[V1] BULUGH AL MARAM-(TAWHEED)-BANGLA_missing.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C357"/>
+  <dimension ref="A1:C359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6477,6 +6477,40 @@
         </is>
       </c>
     </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>1196</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>وَصَحَّ عَنْ عَلِيٍّ مِنْ طُرُقٍ نَحْوُهُ مَوْقُوفًا. أَخْرَجَهُ ابْنُ أَبِي شَيْبَةَ, وَالْحَاكِمُ</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>এটি সহীহ সনদে মাওকূফ হিসেবে বর্ণিত হয়েছে। মুসান্নাফ ইবনু আবূ শায়বাহ, হাকিম।</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>1537</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>وَعَنِ ابْنِ مَسْعُودٍ - رضي الله عنه - قَالَ: قَالَ رَسُولُ اللَّهِ - صلى الله عليه وسلم: «اللَّهُمَّ [ص: 461] كَمَا أَحْسَنْتَ خَلْقِي, فَحَسِّنْ خُلُقِي». رَوَاهُ أَحْمَدُ وَصَحَّحَهُ ابْنُ حِبَّانَ</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ্‌ (সাল্লাল্লাহু ‘আলাইহি ওয়া সাল্লাম) বলেছেনঃ হে আল্লাহ্‌! তুমি আমার গঠন ও আকৃতি যে রকম সুন্দর করেছ, আমার চরিত্রকেও অনুরূপ সুন্দর কর। [১৬৪৫]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
